--- a/data/trans_camb/P68-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P68-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 17,53</t>
+          <t>-5,18; 17,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 28,31</t>
+          <t>6,21; 28,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,56; -4,06</t>
+          <t>-22,91; -4,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 22,13</t>
+          <t>-5,61; 23,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 27,39</t>
+          <t>1,83; 27,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,9; -5,86</t>
+          <t>-25,21; -5,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 15,87</t>
+          <t>-1,65; 15,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,89; 23,92</t>
+          <t>8,09; 24,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,89; -8,31</t>
+          <t>-21,18; -7,98</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 86,33</t>
+          <t>-16,98; 83,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 140,6</t>
+          <t>18,46; 135,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,71; -18,15</t>
+          <t>-71,96; -21,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 114,18</t>
+          <t>-17,37; 120,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 137,41</t>
+          <t>3,26; 149,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,26; -31,42</t>
+          <t>-74,84; -28,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 72,79</t>
+          <t>-6,01; 68,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,07; 107,05</t>
+          <t>26,83; 114,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,55; -36,13</t>
+          <t>-69,21; -35,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 15,24</t>
+          <t>-2,96; 15,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,85; 32,29</t>
+          <t>11,38; 31,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 2,74</t>
+          <t>-14,03; 3,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 15,2</t>
+          <t>-7,99; 14,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 23,25</t>
+          <t>1,89; 24,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 13,58</t>
+          <t>-5,89; 13,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 11,32</t>
+          <t>-1,96; 11,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 25,75</t>
+          <t>10,1; 25,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 4,65</t>
+          <t>-8,32; 4,64</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 62,9</t>
+          <t>-9,73; 68,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,76; 142,79</t>
+          <t>36,95; 140,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,51; 11,54</t>
+          <t>-48,3; 14,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 75,49</t>
+          <t>-26,22; 71,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 118,05</t>
+          <t>6,38; 123,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 69,84</t>
+          <t>-20,04; 70,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 48,98</t>
+          <t>-6,62; 51,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,0; 113,56</t>
+          <t>34,57; 109,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 20,54</t>
+          <t>-28,94; 20,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 5,82</t>
+          <t>-11,53; 4,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 4,92</t>
+          <t>-13,22; 5,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 23,04</t>
+          <t>3,93; 23,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 12,0</t>
+          <t>-13,95; 11,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 3,74</t>
+          <t>-18,12; 3,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 25,46</t>
+          <t>3,52; 26,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 4,64</t>
+          <t>-10,02; 4,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 1,77</t>
+          <t>-12,61; 1,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 21,63</t>
+          <t>6,65; 21,75</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,51; 34,61</t>
+          <t>-47,32; 29,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 28,81</t>
+          <t>-51,52; 30,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,86; 142,08</t>
+          <t>15,91; 141,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 68,47</t>
+          <t>-47,24; 60,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 32,86</t>
+          <t>-66,16; 23,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,27; 159,29</t>
+          <t>8,85; 156,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 26,31</t>
+          <t>-38,5; 27,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,02; 9,94</t>
+          <t>-48,91; 13,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,88; 120,07</t>
+          <t>25,84; 121,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 16,71</t>
+          <t>-2,16; 17,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 13,64</t>
+          <t>-8,16; 13,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 8,51</t>
+          <t>-11,71; 8,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 23,45</t>
+          <t>0,53; 23,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,8; 32,42</t>
+          <t>9,33; 34,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 36,84</t>
+          <t>-6,0; 39,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 16,0</t>
+          <t>1,32; 17,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 17,85</t>
+          <t>1,84; 18,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 22,78</t>
+          <t>-6,84; 23,52</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 73,65</t>
+          <t>-8,32; 77,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 59,27</t>
+          <t>-28,65; 61,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 39,71</t>
+          <t>-40,71; 38,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 182,61</t>
+          <t>0,35; 186,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,98; 246,71</t>
+          <t>40,8; 260,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 252,42</t>
+          <t>-34,67; 265,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 78,82</t>
+          <t>4,88; 85,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 91,54</t>
+          <t>7,11; 91,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 114,6</t>
+          <t>-26,56; 108,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 10,57</t>
+          <t>-12,62; 10,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 10,92</t>
+          <t>-13,49; 10,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 4,61</t>
+          <t>-14,89; 4,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 22,11</t>
+          <t>-8,67; 22,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 8,41</t>
+          <t>-17,19; 8,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 5,09</t>
+          <t>-16,37; 5,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 10,98</t>
+          <t>-7,08; 11,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 5,61</t>
+          <t>-11,98; 5,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 0,96</t>
+          <t>-13,83; 0,9</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 70,88</t>
+          <t>-48,78; 74,65</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 73,53</t>
+          <t>-53,27; 71,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 29,48</t>
+          <t>-55,79; 36,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 337,12</t>
+          <t>-46,51; 341,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,5; 137,03</t>
+          <t>-75,97; 146,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,29; 76,2</t>
+          <t>-65,83; 101,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 75,73</t>
+          <t>-33,02; 84,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-55,41; 40,4</t>
+          <t>-55,05; 38,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 7,76</t>
+          <t>-56,31; 8,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 22,56</t>
+          <t>-1,61; 22,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 6,39</t>
+          <t>-17,33; 5,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 6,16</t>
+          <t>-13,33; 6,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 26,43</t>
+          <t>-4,11; 26,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 3,81</t>
+          <t>-18,15; 2,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,09; 28,87</t>
+          <t>5,5; 29,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,77; 19,83</t>
+          <t>1,92; 19,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 0,97</t>
+          <t>-15,25; 0,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 11,25</t>
+          <t>-2,59; 12,43</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 101,82</t>
+          <t>-5,65; 101,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,28; 30,72</t>
+          <t>-53,64; 25,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 27,88</t>
+          <t>-42,1; 34,2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 229,53</t>
+          <t>-19,98; 225,35</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-78,88; 37,71</t>
+          <t>-82,41; 30,08</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22,54; 275,89</t>
+          <t>17,24; 246,32</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,53; 99,48</t>
+          <t>6,05; 97,42</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 5,95</t>
+          <t>-55,85; 6,07</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 59,43</t>
+          <t>-8,94; 65,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 1,22</t>
+          <t>-13,01; 1,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 2,14</t>
+          <t>-11,3; 2,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 2,51</t>
+          <t>-11,05; 2,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 9,96</t>
+          <t>-7,24; 10,12</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 3,28</t>
+          <t>-12,89; 3,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 6,86</t>
+          <t>-9,47; 6,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 2,14</t>
+          <t>-9,36; 2,12</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 0,26</t>
+          <t>-9,64; 0,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 2,25</t>
+          <t>-7,44; 2,58</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-43,49; 6,06</t>
+          <t>-44,81; 4,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,42; 9,14</t>
+          <t>-37,4; 10,25</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 11,09</t>
+          <t>-35,94; 11,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 49,33</t>
+          <t>-25,46; 52,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 16,91</t>
+          <t>-43,54; 21,41</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 37,36</t>
+          <t>-29,78; 36,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,82; 9,45</t>
+          <t>-32,73; 9,41</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 1,44</t>
+          <t>-34,12; 2,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 10,75</t>
+          <t>-27,07; 10,99</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -5,07</t>
+          <t>-16,46; -5,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -6,23</t>
+          <t>-17,22; -6,21</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,24; -6,93</t>
+          <t>-23,81; -7,82</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -2,01</t>
+          <t>-15,53; -1,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -5,19</t>
+          <t>-18,13; -5,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 7,0</t>
+          <t>-8,12; 7,03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -5,71</t>
+          <t>-14,59; -5,99</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,15; -7,85</t>
+          <t>-16,44; -7,98</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-18,66; -4,37</t>
+          <t>-18,98; -4,73</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-60,56; -23,86</t>
+          <t>-60,93; -24,34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-64,74; -28,74</t>
+          <t>-65,27; -27,61</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,38; -30,15</t>
+          <t>-86,29; -34,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-64,9; -10,12</t>
+          <t>-64,34; -4,99</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-75,58; -28,79</t>
+          <t>-73,92; -31,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 42,03</t>
+          <t>-31,95; 40,71</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-58,02; -28,0</t>
+          <t>-57,84; -29,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-64,25; -36,71</t>
+          <t>-65,38; -38,3</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-73,02; -20,15</t>
+          <t>-77,12; -21,35</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,7</t>
+          <t>-4,52; 1,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,84</t>
+          <t>-3,12; 3,26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,94; -3,5</t>
+          <t>-13,97; -3,54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,88</t>
+          <t>-2,52; 5,0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,13</t>
+          <t>-4,14; 2,75</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 9,03</t>
+          <t>-1,67; 8,79</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,95</t>
+          <t>-2,88; 1,93</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,86</t>
+          <t>-2,87; 1,84</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,26</t>
+          <t>-7,81; -0,16</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 7,19</t>
+          <t>-17,35; 6,24</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 11,95</t>
+          <t>-11,86; 14,06</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -14,91</t>
+          <t>-54,49; -14,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 24,42</t>
+          <t>-10,73; 25,53</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 16,29</t>
+          <t>-17,82; 13,79</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 44,25</t>
+          <t>-7,71; 43,07</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 8,58</t>
+          <t>-11,55; 8,51</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 8,37</t>
+          <t>-11,69; 8,21</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -1,14</t>
+          <t>-32,81; -1,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P68-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P68-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-13,65</t>
+          <t>-13,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,87</t>
+          <t>-15,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,18</t>
+          <t>-14,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 17,3</t>
+          <t>-4,46; 16,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 28,34</t>
+          <t>5,67; 27,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,91; -4,77</t>
+          <t>-21,77; -4,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 23,57</t>
+          <t>-6,14; 22,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 27,98</t>
+          <t>0,6; 25,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,21; -5,76</t>
+          <t>-24,54; -5,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 15,57</t>
+          <t>-1,23; 16,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,09; 24,57</t>
+          <t>7,82; 24,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,18; -7,98</t>
+          <t>-20,51; -7,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-52,41%</t>
+          <t>-50,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-57,67%</t>
+          <t>-58,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-54,65%</t>
+          <t>-53,95%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 83,49</t>
+          <t>-16,1; 73,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 135,06</t>
+          <t>18,41; 131,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,96; -21,33</t>
+          <t>-68,4; -21,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 120,39</t>
+          <t>-20,08; 113,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 149,52</t>
+          <t>2,39; 135,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,84; -28,49</t>
+          <t>-73,79; -28,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 68,71</t>
+          <t>-4,13; 72,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,83; 114,15</t>
+          <t>26,01; 110,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,21; -35,11</t>
+          <t>-67,62; -34,29</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,13</t>
+          <t>-6,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 15,81</t>
+          <t>-2,8; 16,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,38; 31,48</t>
+          <t>13,02; 32,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 3,37</t>
+          <t>-14,42; 2,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 14,23</t>
+          <t>-8,42; 13,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 24,75</t>
+          <t>0,98; 24,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 13,66</t>
+          <t>-5,95; 13,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 11,79</t>
+          <t>-3,02; 12,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 25,78</t>
+          <t>10,3; 25,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 4,64</t>
+          <t>-9,19; 3,84</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-22,91%</t>
+          <t>-23,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-8,0%</t>
+          <t>-9,37%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 68,57</t>
+          <t>-10,09; 71,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,95; 140,55</t>
+          <t>42,36; 142,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 14,58</t>
+          <t>-48,83; 12,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 71,88</t>
+          <t>-27,98; 70,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 123,59</t>
+          <t>1,98; 125,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 70,19</t>
+          <t>-19,77; 74,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 51,9</t>
+          <t>-9,6; 52,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,57; 109,81</t>
+          <t>35,34; 113,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 20,09</t>
+          <t>-31,85; 16,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,75</t>
+          <t>12,6</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>14,98</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,91</t>
+          <t>13,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 4,81</t>
+          <t>-11,89; 6,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 5,51</t>
+          <t>-12,82; 6,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 23,82</t>
+          <t>2,45; 21,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 11,64</t>
+          <t>-13,9; 9,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 3,77</t>
+          <t>-19,73; 3,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 26,01</t>
+          <t>2,88; 26,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 4,7</t>
+          <t>-9,49; 4,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 1,75</t>
+          <t>-12,39; 2,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 21,75</t>
+          <t>6,51; 21,18</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 29,89</t>
+          <t>-46,51; 37,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,52; 30,89</t>
+          <t>-51,45; 40,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,91; 141,66</t>
+          <t>7,5; 134,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 60,52</t>
+          <t>-48,72; 63,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,16; 23,22</t>
+          <t>-67,63; 13,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,85; 156,83</t>
+          <t>6,19; 157,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 27,48</t>
+          <t>-39,17; 24,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 13,03</t>
+          <t>-50,0; 11,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,84; 121,64</t>
+          <t>26,52; 120,93</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,33</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>4,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 17,58</t>
+          <t>-2,77; 18,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 13,69</t>
+          <t>-7,41; 14,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 8,31</t>
+          <t>-11,22; 9,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 23,52</t>
+          <t>1,21; 23,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 34,77</t>
+          <t>7,05; 32,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 39,26</t>
+          <t>4,08; 21,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 17,09</t>
+          <t>1,69; 16,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 18,51</t>
+          <t>1,53; 18,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 23,52</t>
+          <t>-2,69; 11,67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-8,3%</t>
+          <t>-2,54%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 77,85</t>
+          <t>-9,19; 82,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 61,39</t>
+          <t>-26,63; 64,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,71; 38,11</t>
+          <t>-37,42; 43,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 186,43</t>
+          <t>3,99; 184,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,8; 260,2</t>
+          <t>29,97; 254,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 265,12</t>
+          <t>15,02; 168,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 85,77</t>
+          <t>4,91; 83,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,11; 91,63</t>
+          <t>5,7; 94,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 108,75</t>
+          <t>-10,27; 60,95</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-5,23</t>
+          <t>-4,87</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-2,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,72</t>
+          <t>-4,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 10,7</t>
+          <t>-12,26; 10,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 10,9</t>
+          <t>-14,42; 9,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 4,94</t>
+          <t>-15,14; 4,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 22,09</t>
+          <t>-6,95; 22,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 8,46</t>
+          <t>-17,05; 8,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 5,69</t>
+          <t>-15,27; 6,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 11,56</t>
+          <t>-8,37; 10,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 5,58</t>
+          <t>-12,74; 6,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 0,9</t>
+          <t>-12,42; 1,86</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-25,18%</t>
+          <t>-23,44%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-27,23%</t>
+          <t>-19,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-30,43%</t>
+          <t>-26,14%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 74,65</t>
+          <t>-48,68; 73,2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 71,39</t>
+          <t>-54,75; 62,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,79; 36,89</t>
+          <t>-55,02; 31,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-46,51; 341,36</t>
+          <t>-38,67; 287,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,97; 146,27</t>
+          <t>-76,12; 136,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 101,6</t>
+          <t>-62,37; 97,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 84,28</t>
+          <t>-36,55; 79,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-55,05; 38,23</t>
+          <t>-52,54; 45,02</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 8,19</t>
+          <t>-51,73; 13,13</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,44</t>
+          <t>-2,7</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,95</t>
+          <t>17,99</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,98</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 22,96</t>
+          <t>-1,66; 21,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 5,2</t>
+          <t>-16,16; 4,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 6,89</t>
+          <t>-12,71; 6,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 26,14</t>
+          <t>-2,25; 26,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 2,97</t>
+          <t>-18,53; 4,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,5; 29,64</t>
+          <t>5,15; 28,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,92; 19,61</t>
+          <t>2,53; 20,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 0,81</t>
+          <t>-15,35; 0,51</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 12,43</t>
+          <t>-2,23; 13,74</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-12,77%</t>
+          <t>-10,01%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>105,49%</t>
+          <t>105,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 101,91</t>
+          <t>-5,27; 102,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 25,39</t>
+          <t>-53,11; 19,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,1; 34,2</t>
+          <t>-41,53; 32,57</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 225,35</t>
+          <t>-12,36; 229,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-82,41; 30,08</t>
+          <t>-80,99; 43,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,24; 246,32</t>
+          <t>21,4; 266,53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,05; 97,42</t>
+          <t>8,45; 105,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 6,07</t>
+          <t>-54,38; 3,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 65,54</t>
+          <t>-7,84; 71,48</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-3,93</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,86</t>
+          <t>-3,06</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 1,04</t>
+          <t>-13,71; 0,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 2,27</t>
+          <t>-10,91; 3,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 2,6</t>
+          <t>-11,07; 3,16</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 10,12</t>
+          <t>-8,05; 10,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 3,83</t>
+          <t>-12,62; 3,69</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 6,91</t>
+          <t>-9,77; 5,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 2,12</t>
+          <t>-8,65; 3,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 0,49</t>
+          <t>-9,86; 0,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 2,58</t>
+          <t>-8,41; 1,88</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-15,83%</t>
+          <t>-14,92%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-3,55%</t>
+          <t>-6,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-11,16%</t>
+          <t>-11,96%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,81; 4,73</t>
+          <t>-46,99; 1,25</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 10,25</t>
+          <t>-37,03; 14,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 11,29</t>
+          <t>-37,55; 14,14</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 52,91</t>
+          <t>-29,12; 51,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 21,41</t>
+          <t>-42,83; 21,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 36,78</t>
+          <t>-31,92; 31,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 9,41</t>
+          <t>-30,79; 13,16</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 2,23</t>
+          <t>-35,08; 4,12</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 10,99</t>
+          <t>-28,74; 8,58</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-14,7</t>
+          <t>-9,08</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-2,37</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,33</t>
+          <t>-6,54</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-16,46; -5,39</t>
+          <t>-16,21; -5,49</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -6,21</t>
+          <t>-17,36; -6,45</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,81; -7,82</t>
+          <t>-13,78; -3,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-15,53; -1,05</t>
+          <t>-15,7; -1,63</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -5,4</t>
+          <t>-18,22; -5,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 7,03</t>
+          <t>-9,51; 3,62</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-14,59; -5,99</t>
+          <t>-14,56; -6,09</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-16,44; -7,98</t>
+          <t>-15,88; -7,36</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -4,73</t>
+          <t>-10,34; -2,93</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-61,93%</t>
+          <t>-38,26%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>-11,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-45,45%</t>
+          <t>-28,76%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-60,93; -24,34</t>
+          <t>-61,24; -25,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,27; -27,61</t>
+          <t>-65,12; -28,79</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-86,29; -34,59</t>
+          <t>-52,97; -17,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-64,34; -4,99</t>
+          <t>-65,24; -10,16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-73,92; -31,37</t>
+          <t>-73,4; -28,72</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 40,71</t>
+          <t>-36,99; 22,25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-57,84; -29,39</t>
+          <t>-58,61; -28,87</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-65,38; -38,3</t>
+          <t>-65,01; -37,28</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-77,12; -21,35</t>
+          <t>-41,63; -14,24</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-7,45</t>
+          <t>-4,75</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-2,28</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,51</t>
+          <t>-4,63; 1,19</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,26</t>
+          <t>-3,41; 2,8</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -3,54</t>
+          <t>-7,93; -1,87</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,0</t>
+          <t>-2,41; 5,15</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,75</t>
+          <t>-4,28; 2,9</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 8,79</t>
+          <t>-1,58; 4,59</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,93</t>
+          <t>-3,19; 1,71</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,84</t>
+          <t>-2,93; 1,91</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -0,16</t>
+          <t>-4,54; -0,17</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-29,88%</t>
+          <t>-19,05%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-13,76%</t>
+          <t>-9,6%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 6,24</t>
+          <t>-17,71; 5,1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 14,06</t>
+          <t>-12,86; 11,97</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -14,68</t>
+          <t>-30,64; -8,17</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 25,53</t>
+          <t>-10,42; 26,19</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 13,79</t>
+          <t>-18,15; 15,28</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 43,07</t>
+          <t>-6,63; 23,49</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 8,51</t>
+          <t>-12,67; 7,55</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 8,21</t>
+          <t>-11,97; 8,49</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-32,81; -1,07</t>
+          <t>-18,03; -0,74</t>
         </is>
       </c>
     </row>
